--- a/dcf/HBM.xlsx
+++ b/dcf/HBM.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,51 +1099,51 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.1374959759807713</v>
+        <v>0.1372561617015858</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.1424959759807713</v>
+        <v>0.1422561617015858</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.1474959759807713</v>
+        <v>0.1472561617015858</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1524959759807713</v>
+        <v>0.1522561617015858</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1574959759807713</v>
+        <v>0.1572561617015859</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1624959759807713</v>
+        <v>0.1622561617015859</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1674959759807713</v>
+        <v>0.1672561617015859</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
         <v>9</v>
       </c>
-      <c r="B5" s="53" t="n">
-        <v>22.0596090721606</v>
+      <c r="B5" s="8" t="n">
+        <v>22.09465482141168</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>21.34573397179775</v>
+        <v>21.37925325449738</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>20.66285697416655</v>
+        <v>20.69492491119808</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>20.00945653282711</v>
+        <v>20.0401441936036</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>19.38409296583998</v>
+        <v>19.41346760446858</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>18.78540369479654</v>
+        <v>18.81352897149031</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>18.21209878058924</v>
+        <v>18.23903496930763</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>23.46120288784147</v>
+        <v>23.49920699734772</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>22.68718267881832</v>
-      </c>
-      <c r="D6" s="53" t="n">
-        <v>21.94698744059977</v>
+        <v>22.7235209671444</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>21.98174215909498</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>21.2389513016899</v>
+        <v>21.27220025666316</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>20.56149820368843</v>
+        <v>20.59331501586771</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>19.91313667087901</v>
+        <v>19.94359101864721</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>19.29245490613798</v>
+        <v>19.321612753625</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>24.86279670352233</v>
+        <v>24.90375917328376</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>24.02863138583889</v>
+        <v>24.06778867979141</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>23.23111790703299</v>
-      </c>
-      <c r="E7" s="53" t="n">
-        <v>22.46844607055269</v>
+        <v>23.26855940699187</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>22.50425631972273</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>21.73890344153686</v>
+        <v>21.77316242726683</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>21.04086964696149</v>
+        <v>21.07365306580411</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>20.37281103168672</v>
+        <v>20.40419053794238</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>26.2643905192032</v>
+        <v>26.3083113492198</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>25.37008009285946</v>
+        <v>25.41205639243841</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>24.51524837346621</v>
+        <v>24.55537665488877</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>23.69794083941548</v>
+        <v>23.7363123827823</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>22.91630867938531</v>
-      </c>
-      <c r="G8" s="53" t="n">
-        <v>22.16860262304396</v>
+        <v>22.95300983866596</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>22.20371511296101</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>21.45316715723546</v>
+        <v>21.48676832225975</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>27.66598433488407</v>
+        <v>27.71286352515584</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>26.71152879988002</v>
+        <v>26.75632410508543</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>25.79937883989942</v>
+        <v>25.84219390278567</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>24.92743560827828</v>
+        <v>24.96836844584186</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>24.09371391723374</v>
+        <v>24.13285725006509</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>23.29633559912643</v>
-      </c>
-      <c r="H9" s="53" t="n">
-        <v>22.53352328278419</v>
+        <v>23.33377716011791</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>22.56934610657713</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>29.06757815056494</v>
+        <v>29.11741570109188</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>28.05297750690059</v>
+        <v>28.10059181773244</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>27.08350930633264</v>
+        <v>27.12901115068257</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>26.15693037714107</v>
+        <v>26.20042450890143</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>25.27111915508219</v>
+        <v>25.31270466146421</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>24.42406857520891</v>
+        <v>24.46383920727481</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>23.61387940833293</v>
+        <v>23.6519238908945</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>30.4691719662458</v>
+        <v>30.52196787702792</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>29.39442621392116</v>
+        <v>29.44485953037945</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>28.36763977276586</v>
+        <v>28.41582839857947</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>27.38642514600386</v>
+        <v>27.432480571961</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>26.44852439293062</v>
+        <v>26.49255207286334</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>25.55180155129138</v>
+        <v>25.59390125443171</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>24.69423553388167</v>
+        <v>24.73450167521187</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>22.59000015258789</v>
+        <v>21.80500030517578</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1524959759807713</v>
+        <v>0.1522561617015858</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.929073839931993</v>
+        <v>0.9291124998701762</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>22.59000015258789</v>
+        <v>21.80500030517578</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>23.69794083941548</v>
+        <v>23.7363123827823</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>32.08781339211942</v>
+        <v>32.14227253356186</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>17.35545965416435</v>
+        <v>17.38185848383027</v>
       </c>
     </row>
     <row r="59">
